--- a/artfynd/A 51647-2025 artfynd.xlsx
+++ b/artfynd/A 51647-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982566</v>
       </c>
       <c r="B2" t="n">
-        <v>109254</v>
+        <v>109264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51647-2025 artfynd.xlsx
+++ b/artfynd/A 51647-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,205 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131561705</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99026</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>538726</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6356771</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gårdveda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131562110</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57888</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>538637</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6356784</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gårdveda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51647-2025 artfynd.xlsx
+++ b/artfynd/A 51647-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>131561705</v>
       </c>
       <c r="B4" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>131562110</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51647-2025 artfynd.xlsx
+++ b/artfynd/A 51647-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>131561705</v>
       </c>
       <c r="B4" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>131562110</v>
       </c>
       <c r="B5" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51647-2025 artfynd.xlsx
+++ b/artfynd/A 51647-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>131561705</v>
       </c>
       <c r="B4" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51647-2025 artfynd.xlsx
+++ b/artfynd/A 51647-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>131561705</v>
       </c>
       <c r="B4" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>131562110</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51647-2025 artfynd.xlsx
+++ b/artfynd/A 51647-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>131561705</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>131562110</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51647-2025 artfynd.xlsx
+++ b/artfynd/A 51647-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>131561705</v>
       </c>
       <c r="B4" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>131562110</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51647-2025 artfynd.xlsx
+++ b/artfynd/A 51647-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>131561705</v>
       </c>
       <c r="B4" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>131562110</v>
       </c>
       <c r="B5" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51647-2025 artfynd.xlsx
+++ b/artfynd/A 51647-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>131561705</v>
       </c>
       <c r="B4" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>131562110</v>
       </c>
       <c r="B5" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51647-2025 artfynd.xlsx
+++ b/artfynd/A 51647-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>131561705</v>
       </c>
       <c r="B4" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>131562110</v>
       </c>
       <c r="B5" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51647-2025 artfynd.xlsx
+++ b/artfynd/A 51647-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73982566</v>
+        <v>131562110</v>
       </c>
       <c r="B2" t="n">
-        <v>109264</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>8 Övra Vrångens NV-spets 200 m NNV t N, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538705</v>
+        <v>538637</v>
       </c>
       <c r="R2" t="n">
-        <v>6356809</v>
+        <v>6356784</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1986-01-01</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1986-12-31</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6F1i 3502. SOM: Hypochoeris maculata. LEG: Dag Hansen, Edit Carlsson, John Kraft</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,57 +761,43 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Skogsväg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100712201</v>
+        <v>100712493</v>
       </c>
       <c r="B3" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>220075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538676.4192644223</v>
+        <v>538591</v>
       </c>
       <c r="R3" t="n">
-        <v>6356707.186914951</v>
+        <v>6356751</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,19 +847,14 @@
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,48 +881,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131561705</v>
+        <v>73982566</v>
       </c>
       <c r="B4" t="n">
-        <v>99054</v>
+        <v>109814</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>220204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>8 Övra Vrångens NV-spets 200 m NNV t N, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538726</v>
+        <v>538705</v>
       </c>
       <c r="R4" t="n">
-        <v>6356771</v>
+        <v>6356809</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,12 +946,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>1986-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>1986-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6F1i 3502. SOM: Hypochoeris maculata. LEG: Dag Hansen, Edit Carlsson, John Kraft</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,48 +967,57 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Skogsväg</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131562110</v>
+        <v>131561524</v>
       </c>
       <c r="B5" t="n">
-        <v>57911</v>
+        <v>99195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538637</v>
+        <v>538774</v>
       </c>
       <c r="R5" t="n">
-        <v>6356784</v>
+        <v>6356797</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1070,11 +1065,6 @@
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1096,6 +1086,295 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131561705</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>538726</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6356771</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gårdveda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131562512</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106313</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220827</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallört (aggregat)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Monotropa hypopitys agg.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>538616</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6356888</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gårdveda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100712201</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>538676</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6356707</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gårdveda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51647-2025 artfynd.xlsx
+++ b/artfynd/A 51647-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131562110</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100712493</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73982566</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131561524</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131561705</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131562512</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,8 +1410,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100712201</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>